--- a/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/updateWorkoutSessionWithExercises-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/updateWorkoutSessionWithExercises-it-form.xlsx
@@ -367,7 +367,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="20726400" cy="6757987"/>
+    <xdr:ext cx="20726400" cy="7239000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -849,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="36" width="11" customWidth="1"/>
@@ -889,6 +889,8 @@
     <row r="32" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
